--- a/3、电流环建模/D轴同步电感/D轴同步电感特性曲线.xlsx
+++ b/3、电流环建模/D轴同步电感/D轴同步电感特性曲线.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\个人资源\大学学习\课外项目与专业软件资料\FOC\参数测量\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\个人资源\大学学习\课外项目与专业软件资料\FOC\数据处理\3、电流环建模\D轴同步电感\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5BBBB7-25F6-4E29-AE88-56CA44DD7A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D5A067-1B62-4227-9BD5-02CBC9C3103B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -305,67 +305,67 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>2.4404981835140003</c:v>
+                  <c:v>2.3227099999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.2772148440689999</c:v>
+                  <c:v>2.34741</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.4819100000000001</c:v>
+                  <c:v>2.29122</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.467523952424</c:v>
+                  <c:v>2.2113</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.2992131556550004</c:v>
+                  <c:v>2.20817</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.458112963044</c:v>
+                  <c:v>2.2027999999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.3559100000000002</c:v>
+                  <c:v>2.1794699999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.4203473339810002</c:v>
+                  <c:v>2.0969899999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.3153178259449998</c:v>
+                  <c:v>2.0760200000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.0807053011410002</c:v>
+                  <c:v>2.0170499999999998</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.09206</c:v>
+                  <c:v>1.8615200000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.1104071493089998</c:v>
+                  <c:v>1.88628</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.0365327781900002</c:v>
+                  <c:v>1.9021699999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.0326750244439999</c:v>
+                  <c:v>1.84108</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.92604</c:v>
+                  <c:v>1.80467</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.9273919394750001</c:v>
+                  <c:v>1.70831</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.0393590965210002</c:v>
+                  <c:v>1.67964</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.842665004663</c:v>
+                  <c:v>1.6679999999999999</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.80419</c:v>
+                  <c:v>1.63713</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.6963984774680001</c:v>
+                  <c:v>1.5678799999999999</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.67742454688</c:v>
+                  <c:v>1.42414</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1545,13 +1545,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1559,188 +1559,172 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>-5</v>
       </c>
       <c r="B2" s="1">
-        <f>0.002440498183514*1000</f>
-        <v>2.4404981835140003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.3227099999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>-4.5</v>
       </c>
       <c r="B3" s="1">
-        <f>0.002277214844069*1000</f>
-        <v>2.2772148440689999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.34741</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>-4</v>
       </c>
       <c r="B4" s="1">
-        <v>2.4819100000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.29122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>-3.5</v>
       </c>
       <c r="B5" s="1">
-        <f>0.002467523952424*1000</f>
-        <v>2.467523952424</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.2113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>-3</v>
       </c>
       <c r="B6" s="1">
-        <f>0.002299213155655*1000</f>
-        <v>2.2992131556550004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.20817</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>-2.5</v>
       </c>
       <c r="B7" s="1">
-        <f>0.002458112963044*1000</f>
-        <v>2.458112963044</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.2027999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>-2</v>
       </c>
       <c r="B8" s="1">
-        <v>2.3559100000000002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.1794699999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>-1.5</v>
       </c>
       <c r="B9" s="1">
-        <f>0.002420347333981*1000</f>
-        <v>2.4203473339810002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.0969899999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>-1</v>
       </c>
       <c r="B10" s="1">
-        <f>0.002315317825945*1000</f>
-        <v>2.3153178259449998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.0760200000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>-0.5</v>
       </c>
       <c r="B11" s="1">
-        <f>0.002080705301141*1000</f>
-        <v>2.0807053011410002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.0170499999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>0</v>
       </c>
       <c r="B12" s="1">
-        <v>2.09206</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.8615200000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>0.5</v>
       </c>
       <c r="B13" s="1">
-        <f>0.002110407149309*1000</f>
-        <v>2.1104071493089998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.88628</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>1</v>
       </c>
       <c r="B14" s="1">
-        <f>0.00203653277819*1000</f>
-        <v>2.0365327781900002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.9021699999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>1.5</v>
       </c>
       <c r="B15" s="1">
-        <f>0.002032675024444*1000</f>
-        <v>2.0326750244439999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.84108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
       <c r="B16" s="1">
-        <v>1.92604</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.80467</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2.5</v>
       </c>
       <c r="B17" s="1">
-        <f>0.001927391939475*1000</f>
-        <v>1.9273919394750001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.70831</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>3</v>
       </c>
       <c r="B18" s="1">
-        <f>0.002039359096521*1000</f>
-        <v>2.0393590965210002</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.67964</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>3.5</v>
       </c>
       <c r="B19" s="1">
-        <f>0.001842665004663*1000</f>
-        <v>1.842665004663</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.6679999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>4</v>
       </c>
       <c r="B20" s="1">
-        <v>1.80419</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.63713</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>4.5</v>
       </c>
       <c r="B21" s="1">
-        <f>0.001696398477468*1000</f>
-        <v>1.6963984774680001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.5678799999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>5</v>
       </c>
       <c r="B22" s="1">
-        <f>0.00167742454688*1000</f>
-        <v>1.67742454688</v>
+        <v>1.42414</v>
       </c>
     </row>
   </sheetData>
